--- a/config/yunying/rmbcost.xlsx
+++ b/config/yunying/rmbcost.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="rmbcost" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rmbcost" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>累計280ダイヤを消費</t>
+          <t>累计消费280颗钻石</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>累計1280ダイヤを消費</t>
+          <t>累计消费1280颗钻石</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>累計3280ダイヤを消費</t>
+          <t>累计消费3280颗钻石</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>累計6800ダイヤを消費</t>
+          <t>累计消耗6800颗钻石</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1353,794 +1353,746 @@
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
+          <t>累计消耗13800颗钻石</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>累計消耗13800鑽石</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spend 13,800 total Diamonds</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>13800다이아 누적 소모</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>{gold=10000;52=100;21006=100;card = 30041}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" s="1" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>5002</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>累計280ダイヤを消費</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>累計消耗280鑽石</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spend 280 diamonds in total</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>280다이아 누적 소모</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>{28=1;26=3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>5002</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>累計1280ダイヤを消費</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>累計消耗1280鑽石</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spend 1280 diamonds in total</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1280다이아 누적 소모</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>{27=1;26=5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5002</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3280</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>累計3280ダイヤを消費</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>累計消耗3280鑽石</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spend 3280 diamonds in total</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3280다이아 누적 소모</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>{30=1;25=5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5002</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>6800</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>累計6800ダイヤを消費</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>累計消耗6800鑽石</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spend 6800 diamonds in total</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6800다이아 누적 소모</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>{29=1;25=10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5002</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13800</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
           <t>累計13800ダイヤを消費</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>累計消耗13800鑽石</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Spend 13,800 total Diamonds</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spend 13800 diamonds in total</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>13800다이아 누적 소모</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>{gold=10000;52=100;21006=100;card = 30041}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" s="1" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>5002</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>{24=1;25=15}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="D15" s="1" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5003</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D10" s="1" t="inlineStr">
+      <c r="D16" s="1" t="inlineStr">
         <is>
           <t>累計280ダイヤを消費</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>累計消耗280鑽石</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Spend 280 diamonds in total</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>280다이아 누적 소모</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>{28=1;26=3}</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>5002</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5003</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>1280</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D17" s="1" t="inlineStr">
         <is>
           <t>累計1280ダイヤを消費</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>累計消耗1280鑽石</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Spend 1280 diamonds in total</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>1280다이아 누적 소모</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>{27=1;26=5}</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>5002</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5003</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>3280</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
+      <c r="D18" s="1" t="inlineStr">
         <is>
           <t>累計3280ダイヤを消費</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>累計消耗3280鑽石</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Spend 3280 diamonds in total</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>3280다이아 누적 소모</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>{30=1;25=5}</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>5002</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5003</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>6800</t>
         </is>
       </c>
-      <c r="D13" s="1" t="inlineStr">
+      <c r="D19" s="1" t="inlineStr">
         <is>
           <t>累計6800ダイヤを消費</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>累計消耗6800鑽石</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Spend 6800 diamonds in total</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>6800다이아 누적 소모</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>{29=1;25=10}</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>5002</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5003</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>13800</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="D20" s="1" t="inlineStr">
         <is>
           <t>累計13800ダイヤを消費</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>累計消耗13800鑽石</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Spend 13800 diamonds in total</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>13800다이아 누적 소모</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>{24=1;25=15}</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" s="1" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>5003</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+    <row r="21">
+      <c r="D21" s="1" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5004</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr">
+      <c r="D22" s="1" t="inlineStr">
         <is>
           <t>累計280ダイヤを消費</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>累計消耗280鑽石</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Spend 280 diamonds in total</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>280다이아 누적 소모</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>{28=1;26=3}</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>5003</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5004</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>1280</t>
         </is>
       </c>
-      <c r="D17" s="1" t="inlineStr">
+      <c r="D23" s="1" t="inlineStr">
         <is>
           <t>累計1280ダイヤを消費</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>累計消耗1280鑽石</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Spend 1280 diamonds in total</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>1280다이아 누적 소모</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>{27=1;26=5}</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5003</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>5004</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>3280</t>
         </is>
       </c>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="D24" s="1" t="inlineStr">
         <is>
           <t>累計3280ダイヤを消費</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>累計消耗3280鑽石</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Spend 3280 diamonds in total</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>3280다이아 누적 소모</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>{30=1;25=5}</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>5003</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5004</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>6800</t>
         </is>
       </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="D25" s="1" t="inlineStr">
         <is>
           <t>累計6800ダイヤを消費</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>累計消耗6800鑽石</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Spend 6800 diamonds in total</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>6800다이아 누적 소모</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>{29=1;25=10}</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>5003</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5004</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>13800</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
+      <c r="D26" s="1" t="inlineStr">
         <is>
           <t>累計13800ダイヤを消費</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>累計消耗13800鑽石</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Spend 13800 diamonds in total</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>13800다이아 누적 소모</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>{24=1;25=15}</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" s="1" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>5004</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+    <row r="27">
+      <c r="D27" s="1" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D22" s="1" t="inlineStr">
+      <c r="D28" s="1" t="inlineStr">
         <is>
           <t>累計280ダイヤを消費</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>累計消耗280鑽石</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Spend 280 diamonds in total</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>280다이아 누적 소모</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>{28=1;26=3}</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>5004</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>1280</t>
         </is>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D29" s="1" t="inlineStr">
         <is>
           <t>累計1280ダイヤを消費</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>累計消耗1280鑽石</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Spend 1280 diamonds in total</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>1280다이아 누적 소모</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>{27=1;26=5}</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>5004</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>3280</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="D30" s="1" t="inlineStr">
         <is>
           <t>累計3280ダイヤを消費</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>累計消耗3280鑽石</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Spend 3280 diamonds in total</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>3280다이아 누적 소모</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>{30=1;25=5}</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>5004</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>6800</t>
         </is>
       </c>
-      <c r="D25" s="1" t="inlineStr">
+      <c r="D31" s="1" t="inlineStr">
         <is>
           <t>累計6800ダイヤを消費</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>累計消耗6800鑽石</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Spend 6800 diamonds in total</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>6800다이아 누적 소모</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>{29=1;25=10}</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>5004</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>13800</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>累計13800ダイヤを消費</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>累計消耗13800鑽石</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Spend 13800 diamonds in total</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>13800다이아 누적 소모</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>{24=1;25=15}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" s="1" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>5005</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>累計280ダイヤを消費</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>累計消耗280鑽石</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Spend 280 diamonds in total</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>280다이아 누적 소모</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>{28=1;26=3}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>5005</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>累計1280ダイヤを消費</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>累計消耗1280鑽石</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Spend 1280 diamonds in total</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>1280다이아 누적 소모</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>{27=1;26=5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>5005</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>3280</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t>累計3280ダイヤを消費</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>累計消耗3280鑽石</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Spend 3280 diamonds in total</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>3280다이아 누적 소모</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>{30=1;25=5}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>5005</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>6800</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>累計6800ダイヤを消費</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>累計消耗6800鑽石</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Spend 6800 diamonds in total</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>6800다이아 누적 소모</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>{29=1;25=10}</t>
-        </is>
-      </c>
-    </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
           <t>5005</t>
